--- a/EXCEL/Data/Fravær_data/Fravær_ialt.xlsx
+++ b/EXCEL/Data/Fravær_data/Fravær_ialt.xlsx
@@ -70,7 +70,7 @@
     <t>Datasæt 00 2015</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.54.43</t>
+    <t>Kørsel 14.4.2026 12.27.29</t>
   </si>
   <si>
     <t/>
